--- a/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_Rubin_7000steps_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>158921.058</v>
+        <v>158925.985</v>
       </c>
       <c r="C2">
-        <v>153683.77</v>
+        <v>153687.073</v>
       </c>
       <c r="D2">
-        <v>164158.347</v>
+        <v>164164.896</v>
       </c>
       <c r="E2">
-        <v>1652047.695</v>
+        <v>1652131.035</v>
       </c>
       <c r="F2">
-        <v>1626178.659</v>
+        <v>1626266.279</v>
       </c>
       <c r="G2">
-        <v>1677916.731</v>
+        <v>1677995.791</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>219722343457.115</v>
+        <v>219733427685.75</v>
       </c>
       <c r="L2">
-        <v>216281761689.352</v>
+        <v>216293415147.527</v>
       </c>
       <c r="M2">
-        <v>223162925224.879</v>
+        <v>223173440223.973</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>145741.962</v>
+        <v>145871.39</v>
       </c>
       <c r="C3">
-        <v>142327.863</v>
+        <v>142447.672</v>
       </c>
       <c r="D3">
-        <v>149156.061</v>
+        <v>149295.107</v>
       </c>
       <c r="E3">
-        <v>130546.291</v>
+        <v>130657.695</v>
       </c>
       <c r="F3">
-        <v>127959.6</v>
+        <v>128065.535</v>
       </c>
       <c r="G3">
-        <v>133132.982</v>
+        <v>133249.855</v>
       </c>
       <c r="H3">
-        <v>8118118772.684</v>
+        <v>8125328140.898</v>
       </c>
       <c r="I3">
-        <v>7927946649.77</v>
+        <v>7934620243.926</v>
       </c>
       <c r="J3">
-        <v>8308290895.599</v>
+        <v>8316036037.871</v>
       </c>
       <c r="K3">
-        <v>17362656662.855</v>
+        <v>17377473417.888</v>
       </c>
       <c r="L3">
-        <v>17018626769.349</v>
+        <v>17032716111.265</v>
       </c>
       <c r="M3">
-        <v>17706686556.362</v>
+        <v>17722230724.511</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>130093.251</v>
+        <v>130167.178</v>
       </c>
       <c r="C4">
-        <v>127247.802</v>
+        <v>127330.074</v>
       </c>
       <c r="D4">
-        <v>132938.7</v>
+        <v>133004.282</v>
       </c>
       <c r="E4">
-        <v>193690.295</v>
+        <v>194071.391</v>
       </c>
       <c r="F4">
-        <v>188057.529</v>
+        <v>188480.674</v>
       </c>
       <c r="G4">
-        <v>199323.061</v>
+        <v>199662.108</v>
       </c>
       <c r="H4">
-        <v>1926290769.843</v>
+        <v>1927385403.679</v>
       </c>
       <c r="I4">
-        <v>1884158207.605</v>
+        <v>1885376404.016</v>
       </c>
       <c r="J4">
-        <v>1968423332.081</v>
+        <v>1969394403.342</v>
       </c>
       <c r="K4">
-        <v>25760809220.565</v>
+        <v>25811495036.037</v>
       </c>
       <c r="L4">
-        <v>25011651292.987</v>
+        <v>25067929677.166</v>
       </c>
       <c r="M4">
-        <v>26509967148.144</v>
+        <v>26555060394.909</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>27756.412</v>
+        <v>27774.653</v>
       </c>
       <c r="C5">
-        <v>27125.81</v>
+        <v>27141.059</v>
       </c>
       <c r="D5">
-        <v>28387.015</v>
+        <v>28408.246</v>
       </c>
       <c r="E5">
-        <v>54693.69</v>
+        <v>54681.355</v>
       </c>
       <c r="F5">
-        <v>53340.264</v>
+        <v>53323.887</v>
       </c>
       <c r="G5">
-        <v>56047.117</v>
+        <v>56038.824</v>
       </c>
       <c r="H5">
-        <v>2087309949.75</v>
+        <v>2088681647.876</v>
       </c>
       <c r="I5">
-        <v>2039888014.867</v>
+        <v>2041034769.519</v>
       </c>
       <c r="J5">
-        <v>2134731884.633</v>
+        <v>2136328526.233</v>
       </c>
       <c r="K5">
-        <v>7274260831.41</v>
+        <v>7272620272.29</v>
       </c>
       <c r="L5">
-        <v>7094255138.825</v>
+        <v>7092076909.454</v>
       </c>
       <c r="M5">
-        <v>7454266523.995</v>
+        <v>7453163635.125</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>51072.267</v>
+        <v>51065.517</v>
       </c>
       <c r="C6">
-        <v>49170.499</v>
+        <v>49167.272</v>
       </c>
       <c r="D6">
-        <v>52974.035</v>
+        <v>52963.763</v>
       </c>
       <c r="E6">
-        <v>81752.489</v>
+        <v>81802.06600000001</v>
       </c>
       <c r="F6">
-        <v>79518.336</v>
+        <v>79569.12699999999</v>
       </c>
       <c r="G6">
-        <v>83986.64200000001</v>
+        <v>84035.00599999999</v>
       </c>
       <c r="H6">
-        <v>860005901.859</v>
+        <v>859892247.196</v>
       </c>
       <c r="I6">
-        <v>827982035.189</v>
+        <v>827927690.704</v>
       </c>
       <c r="J6">
-        <v>892029768.53</v>
+        <v>891856803.688</v>
       </c>
       <c r="K6">
-        <v>10873081063.178</v>
+        <v>10879674829.757</v>
       </c>
       <c r="L6">
-        <v>10575938746.108</v>
+        <v>10582693882.737</v>
       </c>
       <c r="M6">
-        <v>11170223380.247</v>
+        <v>11176655776.778</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>616683.361</v>
+        <v>511597.327</v>
       </c>
       <c r="C7">
-        <v>607884.2169999999</v>
+        <v>503634.57</v>
       </c>
       <c r="D7">
-        <v>625482.504</v>
+        <v>519560.083</v>
       </c>
       <c r="E7">
-        <v>1785953.977</v>
+        <v>164684.922</v>
       </c>
       <c r="F7">
-        <v>1741826.838</v>
+        <v>160493.668</v>
       </c>
       <c r="G7">
-        <v>1830081.115</v>
+        <v>168876.175</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>237531878915.207</v>
+        <v>21903094608.12</v>
       </c>
       <c r="L7">
-        <v>231662969501.451</v>
+        <v>21345657893.442</v>
       </c>
       <c r="M7">
-        <v>243400788328.964</v>
+        <v>22460531322.798</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>971347.253</v>
+        <v>866476.0649999999</v>
       </c>
       <c r="C8">
-        <v>953756.191</v>
+        <v>849720.647</v>
       </c>
       <c r="D8">
-        <v>988938.3149999999</v>
+        <v>883231.4809999999</v>
       </c>
       <c r="E8">
-        <v>2246636.742</v>
+        <v>625897.429</v>
       </c>
       <c r="F8">
-        <v>2190702.567</v>
+        <v>609932.8910000001</v>
       </c>
       <c r="G8">
-        <v>2302570.917</v>
+        <v>641861.968</v>
       </c>
       <c r="H8">
-        <v>12991725394.136</v>
+        <v>13001287439.649</v>
       </c>
       <c r="I8">
-        <v>12679974907.431</v>
+        <v>12688959108.165</v>
       </c>
       <c r="J8">
-        <v>13303475880.843</v>
+        <v>13313615771.134</v>
       </c>
       <c r="K8">
-        <v>298802686693.215</v>
+        <v>83244358164.092</v>
       </c>
       <c r="L8">
-        <v>291363441448.72</v>
+        <v>81121074474.064</v>
       </c>
       <c r="M8">
-        <v>306241931937.712</v>
+        <v>85367641854.121</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>1130268.311</v>
+        <v>1025402.05</v>
       </c>
       <c r="C9">
-        <v>1107439.961</v>
+        <v>1003407.72</v>
       </c>
       <c r="D9">
-        <v>1153096.662</v>
+        <v>1047396.377</v>
       </c>
       <c r="E9">
-        <v>3898684.437</v>
+        <v>2278028.464</v>
       </c>
       <c r="F9">
-        <v>3816881.226</v>
+        <v>2236199.17</v>
       </c>
       <c r="G9">
-        <v>3980487.648</v>
+        <v>2319857.759</v>
       </c>
       <c r="H9">
-        <v>12991725394.136</v>
+        <v>13001287439.649</v>
       </c>
       <c r="I9">
-        <v>12679974907.431</v>
+        <v>12688959108.165</v>
       </c>
       <c r="J9">
-        <v>13303475880.843</v>
+        <v>13313615771.134</v>
       </c>
       <c r="K9">
-        <v>518525030150.33</v>
+        <v>302977785849.842</v>
       </c>
       <c r="L9">
-        <v>507645203138.072</v>
+        <v>297414489621.5911</v>
       </c>
       <c r="M9">
-        <v>529404857162.591</v>
+        <v>308541082078.094</v>
       </c>
     </row>
   </sheetData>
